--- a/web/files/港岛-山顶区-Twelve Peaks.xlsx
+++ b/web/files/港岛-山顶区-Twelve Peaks.xlsx
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>4858</v>
+        <v>4661</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>666523000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>137201</v>
+        <v>143000</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>4479</v>
+        <v>4197</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>495100000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>110538</v>
+        <v>117965</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>4945</v>
+        <v>4805</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4471</v>
+        <v>4359</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>352000000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>78730</v>
+        <v>80752</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4391</v>
+        <v>4241</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>506049000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>115247</v>
+        <v>119323</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>4470</v>
+        <v>4327</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>491693000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>109998</v>
+        <v>113634</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5221</v>
+        <v>4784</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>730000000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>139820</v>
+        <v>152592</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3905</v>
+        <v>3657</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>458000000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>117286</v>
+        <v>125239</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3845</v>
+        <v>3744</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>458000000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>119116</v>
+        <v>122329</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3942</v>
+        <v>3759</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>392074000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>99461</v>
+        <v>104303</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>4030</v>
+        <v>3771</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>412638000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>102392</v>
+        <v>109424</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3885</v>
+        <v>3731</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>450000000</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>115830</v>
+        <v>120611</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1373,25 +1373,25 @@
       <c r="B6" s="16" t="inlineStr">
         <is>
           <t>1号屋
-4858呎 (4+房)
+4661呎 (4+房)
 (18年-12月-23日)
 $6.67亿
-$137,201/呎</t>
+$143,000/呎</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
           <t>2号屋
-4479呎 (4+房)
+4197呎 (4+房)
 (18年-08月-05日)
 $4.95亿
-$110,538/呎</t>
+$117,965/呎</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
           <t>3号屋
-4945呎 (4+房)
+4805呎 (4+房)
 (在售)
 招标项目
 -</t>
@@ -1400,28 +1400,28 @@
       <c r="E6" s="16" t="inlineStr">
         <is>
           <t>5号屋
-4471呎 (4+房)
+4359呎 (4+房)
 (25年-10月-23日)
 $3.52亿
-$78,730/呎</t>
+$80,752/呎</t>
         </is>
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
           <t>6号屋
-4391呎 (4+房)
+4241呎 (4+房)
 (15年-02月-26日)
 $5.06亿
-$115,247/呎</t>
+$119,323/呎</t>
         </is>
       </c>
       <c r="G6" s="16" t="inlineStr">
         <is>
           <t>7号屋
-4470呎 (4+房)
+4327呎 (4+房)
 (15年-02月-08日)
 $4.92亿
-$109,998/呎</t>
+$113,634/呎</t>
         </is>
       </c>
     </row>
@@ -1434,55 +1434,55 @@
       <c r="B7" s="16" t="inlineStr">
         <is>
           <t>8号屋
-5221呎 (4+房)
+4784呎 (4+房)
 (18年-08月-06日)
 $7.30亿
-$139,820/呎</t>
+$152,592/呎</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
           <t>9号屋
-3905呎 (4+房)
+3657呎 (4+房)
 (18年-12月-27日)
 $4.58亿
-$117,286/呎</t>
+$125,239/呎</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
           <t>10号屋
-3845呎 (3房)
+3744呎 (3房)
 (18年-12月-23日)
 $4.58亿
-$119,116/呎</t>
+$122,329/呎</t>
         </is>
       </c>
       <c r="E7" s="16" t="inlineStr">
         <is>
           <t>11号屋
-3942呎 (4+房)
+3759呎 (4+房)
 (15年-02月-12日)
 $3.92亿
-$99,461/呎</t>
+$104,303/呎</t>
         </is>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
           <t>12号屋
-4030呎 (3房)
+3771呎 (3房)
 (14年-08月-14日)
 $4.13亿
-$102,392/呎</t>
+$109,424/呎</t>
         </is>
       </c>
       <c r="G7" s="16" t="inlineStr">
         <is>
           <t>15号屋
-3885呎 (4+房)
+3731呎 (4+房)
 (18年-11月-08日)
 $4.50亿
-$115,830/呎</t>
+$120,611/呎</t>
         </is>
       </c>
     </row>
